--- a/artfynd/A 13696-2023 artfynd.xlsx
+++ b/artfynd/A 13696-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 13696-2023 artfynd.xlsx
+++ b/artfynd/A 13696-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1767,6 +1767,1580 @@
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>120318861</v>
+      </c>
+      <c r="B11" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Holmnäset, Mpd</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>514780</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6925538</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2023-10-18</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2023-10-18</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Emelie Westin</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Emelie Westin</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>120318864</v>
+      </c>
+      <c r="B12" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Holmnäset, Mpd</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>514913</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6925660</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2023-10-18</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2023-10-18</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Emelie Westin</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Emelie Westin</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>120318858</v>
+      </c>
+      <c r="B13" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Holmnäset, Mpd</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>515035</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6925466</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2023-10-18</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2023-10-18</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Emelie Westin</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Emelie Westin</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>120318860</v>
+      </c>
+      <c r="B14" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Holmnäset, Mpd</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>514791</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6925520</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2023-10-18</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2023-10-18</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Emelie Westin</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Emelie Westin</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>120318859</v>
+      </c>
+      <c r="B15" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Holmnäset, Mpd</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>515027</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6925459</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2023-10-18</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2023-10-18</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Emelie Westin</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Emelie Westin</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>120318862</v>
+      </c>
+      <c r="B16" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Holmnäset, Mpd</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>514696</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6925628</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2023-10-18</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2023-10-18</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Emelie Westin</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Emelie Westin</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>120318850</v>
+      </c>
+      <c r="B17" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Holmnäset, Mpd</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>514866</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6925169</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2023-08-21</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2023-08-21</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Emelie Westin</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Emelie Westin</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>120318853</v>
+      </c>
+      <c r="B18" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Holmnäset, Mpd</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>514985</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6925284</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2023-08-21</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2023-08-21</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Emelie Westin</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Emelie Westin</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>120318851</v>
+      </c>
+      <c r="B19" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Holmnäset, Mpd</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>514665</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6925321</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2023-10-18</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2023-10-18</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Emelie Westin</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Emelie Westin</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>120318855</v>
+      </c>
+      <c r="B20" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Holmnäset, Mpd</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>515227</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6925317</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2023-10-18</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2023-10-18</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Emelie Westin</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Emelie Westin</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>120318854</v>
+      </c>
+      <c r="B21" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Holmnäset, Mpd</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>515015</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6925264</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2023-08-21</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2023-08-21</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Emelie Westin</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Emelie Westin</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>120318857</v>
+      </c>
+      <c r="B22" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Holmnäset, Mpd</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>515094</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6925430</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2023-10-18</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2023-10-18</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Emelie Westin</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Emelie Westin</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>120318866</v>
+      </c>
+      <c r="B23" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Holmnäset, Mpd</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>514990</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6925841</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2023-10-18</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2023-10-18</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Emelie Westin</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Emelie Westin</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>120318856</v>
+      </c>
+      <c r="B24" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Holmnäset, Mpd</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>515159</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6925502</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2023-08-21</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2023-08-21</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Emelie Westin</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Emelie Westin</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>120318863</v>
+      </c>
+      <c r="B25" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Holmnäset, Mpd</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>514693</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6925638</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2023-10-18</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2023-10-18</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Emelie Westin</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Emelie Westin</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 13696-2023 artfynd.xlsx
+++ b/artfynd/A 13696-2023 artfynd.xlsx
@@ -1769,10 +1769,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120318861</v>
+        <v>120318859</v>
       </c>
       <c r="B11" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1804,7 +1804,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>56</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1813,10 +1813,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>514780</v>
+        <v>515027</v>
       </c>
       <c r="R11" t="n">
-        <v>6925538</v>
+        <v>6925459</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1875,10 +1875,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120318864</v>
+        <v>120318863</v>
       </c>
       <c r="B12" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1910,7 +1910,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>27</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1919,10 +1919,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>514913</v>
+        <v>514693</v>
       </c>
       <c r="R12" t="n">
-        <v>6925660</v>
+        <v>6925638</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1981,10 +1981,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120318858</v>
+        <v>120318862</v>
       </c>
       <c r="B13" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2016,7 +2016,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>18</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2025,10 +2025,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>515035</v>
+        <v>514696</v>
       </c>
       <c r="R13" t="n">
-        <v>6925466</v>
+        <v>6925628</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2090,7 +2090,7 @@
         <v>120318860</v>
       </c>
       <c r="B14" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2193,10 +2193,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120318859</v>
+        <v>120318850</v>
       </c>
       <c r="B15" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2226,21 +2226,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Holmnäset, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>515027</v>
+        <v>514866</v>
       </c>
       <c r="R15" t="n">
-        <v>6925459</v>
+        <v>6925169</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2267,12 +2263,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2023-10-18</t>
+          <t>2023-08-21</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2023-10-18</t>
+          <t>2023-08-21</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2299,10 +2295,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120318862</v>
+        <v>120318851</v>
       </c>
       <c r="B16" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2334,7 +2330,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2343,10 +2339,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>514696</v>
+        <v>514665</v>
       </c>
       <c r="R16" t="n">
-        <v>6925628</v>
+        <v>6925321</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2405,10 +2401,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120318850</v>
+        <v>120318856</v>
       </c>
       <c r="B17" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2445,10 +2441,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>514866</v>
+        <v>515159</v>
       </c>
       <c r="R17" t="n">
-        <v>6925169</v>
+        <v>6925502</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2510,7 +2506,7 @@
         <v>120318853</v>
       </c>
       <c r="B18" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2609,10 +2605,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120318851</v>
+        <v>120318854</v>
       </c>
       <c r="B19" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2642,21 +2638,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Holmnäset, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>514665</v>
+        <v>515015</v>
       </c>
       <c r="R19" t="n">
-        <v>6925321</v>
+        <v>6925264</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2683,12 +2675,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2023-10-18</t>
+          <t>2023-08-21</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2023-10-18</t>
+          <t>2023-08-21</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2715,10 +2707,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120318855</v>
+        <v>120318864</v>
       </c>
       <c r="B20" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2750,7 +2742,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2759,10 +2751,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>515227</v>
+        <v>514913</v>
       </c>
       <c r="R20" t="n">
-        <v>6925317</v>
+        <v>6925660</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2821,10 +2813,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120318854</v>
+        <v>120318866</v>
       </c>
       <c r="B21" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2854,17 +2846,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Holmnäset, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>515015</v>
+        <v>514990</v>
       </c>
       <c r="R21" t="n">
-        <v>6925264</v>
+        <v>6925841</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2891,12 +2887,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2023-08-21</t>
+          <t>2023-10-18</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2023-08-21</t>
+          <t>2023-10-18</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2923,10 +2919,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120318857</v>
+        <v>120318861</v>
       </c>
       <c r="B22" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2958,7 +2954,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>13</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2967,10 +2963,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>515094</v>
+        <v>514780</v>
       </c>
       <c r="R22" t="n">
-        <v>6925430</v>
+        <v>6925538</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3029,10 +3025,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120318866</v>
+        <v>120318858</v>
       </c>
       <c r="B23" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3064,7 +3060,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>27</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3073,10 +3069,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>514990</v>
+        <v>515035</v>
       </c>
       <c r="R23" t="n">
-        <v>6925841</v>
+        <v>6925466</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3135,10 +3131,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120318856</v>
+        <v>120318855</v>
       </c>
       <c r="B24" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3168,17 +3164,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Holmnäset, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>515159</v>
+        <v>515227</v>
       </c>
       <c r="R24" t="n">
-        <v>6925502</v>
+        <v>6925317</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3205,12 +3205,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2023-08-21</t>
+          <t>2023-10-18</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2023-08-21</t>
+          <t>2023-10-18</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3237,10 +3237,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120318863</v>
+        <v>120318857</v>
       </c>
       <c r="B25" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3272,7 +3272,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3281,10 +3281,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>514693</v>
+        <v>515094</v>
       </c>
       <c r="R25" t="n">
-        <v>6925638</v>
+        <v>6925430</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>

--- a/artfynd/A 13696-2023 artfynd.xlsx
+++ b/artfynd/A 13696-2023 artfynd.xlsx
@@ -1769,7 +1769,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120318859</v>
+        <v>120318860</v>
       </c>
       <c r="B11" t="n">
         <v>97930</v>
@@ -1804,7 +1804,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1813,10 +1813,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>515027</v>
+        <v>514791</v>
       </c>
       <c r="R11" t="n">
-        <v>6925459</v>
+        <v>6925520</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1875,7 +1875,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120318863</v>
+        <v>120318859</v>
       </c>
       <c r="B12" t="n">
         <v>97930</v>
@@ -1910,7 +1910,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>56</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1919,10 +1919,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>514693</v>
+        <v>515027</v>
       </c>
       <c r="R12" t="n">
-        <v>6925638</v>
+        <v>6925459</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1981,7 +1981,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120318862</v>
+        <v>120318857</v>
       </c>
       <c r="B13" t="n">
         <v>97930</v>
@@ -2016,7 +2016,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2025,10 +2025,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>514696</v>
+        <v>515094</v>
       </c>
       <c r="R13" t="n">
-        <v>6925628</v>
+        <v>6925430</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2087,7 +2087,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120318860</v>
+        <v>120318850</v>
       </c>
       <c r="B14" t="n">
         <v>97930</v>
@@ -2120,21 +2120,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Holmnäset, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>514791</v>
+        <v>514866</v>
       </c>
       <c r="R14" t="n">
-        <v>6925520</v>
+        <v>6925169</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2161,12 +2157,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2023-10-18</t>
+          <t>2023-08-21</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2023-10-18</t>
+          <t>2023-08-21</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2193,7 +2189,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120318850</v>
+        <v>120318854</v>
       </c>
       <c r="B15" t="n">
         <v>97930</v>
@@ -2233,10 +2229,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>514866</v>
+        <v>515015</v>
       </c>
       <c r="R15" t="n">
-        <v>6925169</v>
+        <v>6925264</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2295,7 +2291,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120318851</v>
+        <v>120318866</v>
       </c>
       <c r="B16" t="n">
         <v>97930</v>
@@ -2330,7 +2326,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2339,10 +2335,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>514665</v>
+        <v>514990</v>
       </c>
       <c r="R16" t="n">
-        <v>6925321</v>
+        <v>6925841</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2503,7 +2499,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120318853</v>
+        <v>120318858</v>
       </c>
       <c r="B18" t="n">
         <v>97930</v>
@@ -2536,17 +2532,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Holmnäset, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>514985</v>
+        <v>515035</v>
       </c>
       <c r="R18" t="n">
-        <v>6925284</v>
+        <v>6925466</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2573,12 +2573,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2023-08-21</t>
+          <t>2023-10-18</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2023-08-21</t>
+          <t>2023-10-18</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2605,7 +2605,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120318854</v>
+        <v>120318851</v>
       </c>
       <c r="B19" t="n">
         <v>97930</v>
@@ -2638,17 +2638,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Holmnäset, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>515015</v>
+        <v>514665</v>
       </c>
       <c r="R19" t="n">
-        <v>6925264</v>
+        <v>6925321</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2675,12 +2679,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2023-08-21</t>
+          <t>2023-10-18</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2023-08-21</t>
+          <t>2023-10-18</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2813,7 +2817,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120318866</v>
+        <v>120318855</v>
       </c>
       <c r="B21" t="n">
         <v>97930</v>
@@ -2848,7 +2852,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>91</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2857,10 +2861,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>514990</v>
+        <v>515227</v>
       </c>
       <c r="R21" t="n">
-        <v>6925841</v>
+        <v>6925317</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3025,7 +3029,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120318858</v>
+        <v>120318853</v>
       </c>
       <c r="B23" t="n">
         <v>97930</v>
@@ -3058,21 +3062,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Holmnäset, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>515035</v>
+        <v>514985</v>
       </c>
       <c r="R23" t="n">
-        <v>6925466</v>
+        <v>6925284</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3099,12 +3099,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2023-10-18</t>
+          <t>2023-08-21</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2023-10-18</t>
+          <t>2023-08-21</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3131,7 +3131,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120318855</v>
+        <v>120318863</v>
       </c>
       <c r="B24" t="n">
         <v>97930</v>
@@ -3166,7 +3166,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>27</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3175,10 +3175,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>515227</v>
+        <v>514693</v>
       </c>
       <c r="R24" t="n">
-        <v>6925317</v>
+        <v>6925638</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3237,7 +3237,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120318857</v>
+        <v>120318862</v>
       </c>
       <c r="B25" t="n">
         <v>97930</v>
@@ -3272,7 +3272,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>18</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3281,10 +3281,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>515094</v>
+        <v>514696</v>
       </c>
       <c r="R25" t="n">
-        <v>6925430</v>
+        <v>6925628</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>

--- a/artfynd/A 13696-2023 artfynd.xlsx
+++ b/artfynd/A 13696-2023 artfynd.xlsx
@@ -1769,7 +1769,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120318860</v>
+        <v>120318862</v>
       </c>
       <c r="B11" t="n">
         <v>97930</v>
@@ -1804,7 +1804,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>18</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1813,10 +1813,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>514791</v>
+        <v>514696</v>
       </c>
       <c r="R11" t="n">
-        <v>6925520</v>
+        <v>6925628</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1875,7 +1875,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120318859</v>
+        <v>120318858</v>
       </c>
       <c r="B12" t="n">
         <v>97930</v>
@@ -1910,7 +1910,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>27</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1919,10 +1919,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>515027</v>
+        <v>515035</v>
       </c>
       <c r="R12" t="n">
-        <v>6925459</v>
+        <v>6925466</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1981,7 +1981,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120318857</v>
+        <v>120318854</v>
       </c>
       <c r="B13" t="n">
         <v>97930</v>
@@ -2014,21 +2014,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Holmnäset, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>515094</v>
+        <v>515015</v>
       </c>
       <c r="R13" t="n">
-        <v>6925430</v>
+        <v>6925264</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2055,12 +2051,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2023-10-18</t>
+          <t>2023-08-21</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2023-10-18</t>
+          <t>2023-08-21</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2087,7 +2083,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120318850</v>
+        <v>120318860</v>
       </c>
       <c r="B14" t="n">
         <v>97930</v>
@@ -2120,17 +2116,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Holmnäset, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>514866</v>
+        <v>514791</v>
       </c>
       <c r="R14" t="n">
-        <v>6925169</v>
+        <v>6925520</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2157,12 +2157,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2023-08-21</t>
+          <t>2023-10-18</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2023-08-21</t>
+          <t>2023-10-18</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2189,7 +2189,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120318854</v>
+        <v>120318861</v>
       </c>
       <c r="B15" t="n">
         <v>97930</v>
@@ -2222,17 +2222,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Holmnäset, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>515015</v>
+        <v>514780</v>
       </c>
       <c r="R15" t="n">
-        <v>6925264</v>
+        <v>6925538</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2259,12 +2263,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2023-08-21</t>
+          <t>2023-10-18</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2023-08-21</t>
+          <t>2023-10-18</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2291,7 +2295,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120318866</v>
+        <v>120318864</v>
       </c>
       <c r="B16" t="n">
         <v>97930</v>
@@ -2326,7 +2330,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2335,10 +2339,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>514990</v>
+        <v>514913</v>
       </c>
       <c r="R16" t="n">
-        <v>6925841</v>
+        <v>6925660</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2397,7 +2401,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120318856</v>
+        <v>120318853</v>
       </c>
       <c r="B17" t="n">
         <v>97930</v>
@@ -2437,10 +2441,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>515159</v>
+        <v>514985</v>
       </c>
       <c r="R17" t="n">
-        <v>6925502</v>
+        <v>6925284</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2499,7 +2503,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120318858</v>
+        <v>120318851</v>
       </c>
       <c r="B18" t="n">
         <v>97930</v>
@@ -2534,7 +2538,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2543,10 +2547,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>515035</v>
+        <v>514665</v>
       </c>
       <c r="R18" t="n">
-        <v>6925466</v>
+        <v>6925321</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2605,7 +2609,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120318851</v>
+        <v>120318850</v>
       </c>
       <c r="B19" t="n">
         <v>97930</v>
@@ -2638,21 +2642,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Holmnäset, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>514665</v>
+        <v>514866</v>
       </c>
       <c r="R19" t="n">
-        <v>6925321</v>
+        <v>6925169</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2023-10-18</t>
+          <t>2023-08-21</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2023-10-18</t>
+          <t>2023-08-21</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2711,7 +2711,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120318864</v>
+        <v>120318857</v>
       </c>
       <c r="B20" t="n">
         <v>97930</v>
@@ -2746,7 +2746,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2755,10 +2755,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>514913</v>
+        <v>515094</v>
       </c>
       <c r="R20" t="n">
-        <v>6925660</v>
+        <v>6925430</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2817,7 +2817,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120318855</v>
+        <v>120318866</v>
       </c>
       <c r="B21" t="n">
         <v>97930</v>
@@ -2852,7 +2852,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2861,10 +2861,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>515227</v>
+        <v>514990</v>
       </c>
       <c r="R21" t="n">
-        <v>6925317</v>
+        <v>6925841</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2923,7 +2923,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120318861</v>
+        <v>120318859</v>
       </c>
       <c r="B22" t="n">
         <v>97930</v>
@@ -2958,7 +2958,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>56</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2967,10 +2967,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>514780</v>
+        <v>515027</v>
       </c>
       <c r="R22" t="n">
-        <v>6925538</v>
+        <v>6925459</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3029,7 +3029,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120318853</v>
+        <v>120318863</v>
       </c>
       <c r="B23" t="n">
         <v>97930</v>
@@ -3062,17 +3062,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Holmnäset, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>514985</v>
+        <v>514693</v>
       </c>
       <c r="R23" t="n">
-        <v>6925284</v>
+        <v>6925638</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3099,12 +3103,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2023-08-21</t>
+          <t>2023-10-18</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2023-08-21</t>
+          <t>2023-10-18</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3131,7 +3135,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120318863</v>
+        <v>120318855</v>
       </c>
       <c r="B24" t="n">
         <v>97930</v>
@@ -3166,7 +3170,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>91</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3175,10 +3179,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>514693</v>
+        <v>515227</v>
       </c>
       <c r="R24" t="n">
-        <v>6925638</v>
+        <v>6925317</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3237,7 +3241,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120318862</v>
+        <v>120318856</v>
       </c>
       <c r="B25" t="n">
         <v>97930</v>
@@ -3270,21 +3274,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Holmnäset, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>514696</v>
+        <v>515159</v>
       </c>
       <c r="R25" t="n">
-        <v>6925628</v>
+        <v>6925502</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3311,12 +3311,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2023-10-18</t>
+          <t>2023-08-21</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2023-10-18</t>
+          <t>2023-08-21</t>
         </is>
       </c>
       <c r="AD25" t="b">

--- a/artfynd/A 13696-2023 artfynd.xlsx
+++ b/artfynd/A 13696-2023 artfynd.xlsx
@@ -1769,7 +1769,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120318862</v>
+        <v>120318863</v>
       </c>
       <c r="B11" t="n">
         <v>97930</v>
@@ -1804,7 +1804,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>27</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1813,10 +1813,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>514696</v>
+        <v>514693</v>
       </c>
       <c r="R11" t="n">
-        <v>6925628</v>
+        <v>6925638</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1875,7 +1875,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120318858</v>
+        <v>120318864</v>
       </c>
       <c r="B12" t="n">
         <v>97930</v>
@@ -1910,7 +1910,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1919,10 +1919,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>515035</v>
+        <v>514913</v>
       </c>
       <c r="R12" t="n">
-        <v>6925466</v>
+        <v>6925660</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1981,7 +1981,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120318854</v>
+        <v>120318853</v>
       </c>
       <c r="B13" t="n">
         <v>97930</v>
@@ -2021,10 +2021,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>515015</v>
+        <v>514985</v>
       </c>
       <c r="R13" t="n">
-        <v>6925264</v>
+        <v>6925284</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2083,7 +2083,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120318860</v>
+        <v>120318866</v>
       </c>
       <c r="B14" t="n">
         <v>97930</v>
@@ -2118,7 +2118,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2127,10 +2127,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>514791</v>
+        <v>514990</v>
       </c>
       <c r="R14" t="n">
-        <v>6925520</v>
+        <v>6925841</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2189,7 +2189,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120318861</v>
+        <v>120318855</v>
       </c>
       <c r="B15" t="n">
         <v>97930</v>
@@ -2224,7 +2224,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>91</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2233,10 +2233,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>514780</v>
+        <v>515227</v>
       </c>
       <c r="R15" t="n">
-        <v>6925538</v>
+        <v>6925317</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2295,7 +2295,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120318864</v>
+        <v>120318854</v>
       </c>
       <c r="B16" t="n">
         <v>97930</v>
@@ -2328,21 +2328,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Holmnäset, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>514913</v>
+        <v>515015</v>
       </c>
       <c r="R16" t="n">
-        <v>6925660</v>
+        <v>6925264</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2369,12 +2365,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2023-10-18</t>
+          <t>2023-08-21</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2023-10-18</t>
+          <t>2023-08-21</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2401,7 +2397,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120318853</v>
+        <v>120318858</v>
       </c>
       <c r="B17" t="n">
         <v>97930</v>
@@ -2434,17 +2430,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Holmnäset, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>514985</v>
+        <v>515035</v>
       </c>
       <c r="R17" t="n">
-        <v>6925284</v>
+        <v>6925466</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2471,12 +2471,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2023-08-21</t>
+          <t>2023-10-18</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2023-08-21</t>
+          <t>2023-10-18</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2503,7 +2503,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120318851</v>
+        <v>120318859</v>
       </c>
       <c r="B18" t="n">
         <v>97930</v>
@@ -2538,7 +2538,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>56</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2547,10 +2547,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>514665</v>
+        <v>515027</v>
       </c>
       <c r="R18" t="n">
-        <v>6925321</v>
+        <v>6925459</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2609,7 +2609,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120318850</v>
+        <v>120318861</v>
       </c>
       <c r="B19" t="n">
         <v>97930</v>
@@ -2642,17 +2642,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Holmnäset, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>514866</v>
+        <v>514780</v>
       </c>
       <c r="R19" t="n">
-        <v>6925169</v>
+        <v>6925538</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2679,12 +2683,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2023-08-21</t>
+          <t>2023-10-18</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2023-08-21</t>
+          <t>2023-10-18</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2711,7 +2715,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120318857</v>
+        <v>120318856</v>
       </c>
       <c r="B20" t="n">
         <v>97930</v>
@@ -2744,21 +2748,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Holmnäset, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>515094</v>
+        <v>515159</v>
       </c>
       <c r="R20" t="n">
-        <v>6925430</v>
+        <v>6925502</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2785,12 +2785,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2023-10-18</t>
+          <t>2023-08-21</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2023-10-18</t>
+          <t>2023-08-21</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2817,7 +2817,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120318866</v>
+        <v>120318860</v>
       </c>
       <c r="B21" t="n">
         <v>97930</v>
@@ -2852,7 +2852,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2861,10 +2861,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>514990</v>
+        <v>514791</v>
       </c>
       <c r="R21" t="n">
-        <v>6925841</v>
+        <v>6925520</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2923,7 +2923,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120318859</v>
+        <v>120318862</v>
       </c>
       <c r="B22" t="n">
         <v>97930</v>
@@ -2958,7 +2958,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>18</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2967,10 +2967,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>515027</v>
+        <v>514696</v>
       </c>
       <c r="R22" t="n">
-        <v>6925459</v>
+        <v>6925628</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3029,7 +3029,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120318863</v>
+        <v>120318850</v>
       </c>
       <c r="B23" t="n">
         <v>97930</v>
@@ -3062,21 +3062,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Holmnäset, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>514693</v>
+        <v>514866</v>
       </c>
       <c r="R23" t="n">
-        <v>6925638</v>
+        <v>6925169</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3103,12 +3099,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2023-10-18</t>
+          <t>2023-08-21</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2023-10-18</t>
+          <t>2023-08-21</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3135,7 +3131,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120318855</v>
+        <v>120318851</v>
       </c>
       <c r="B24" t="n">
         <v>97930</v>
@@ -3170,7 +3166,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3179,10 +3175,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>515227</v>
+        <v>514665</v>
       </c>
       <c r="R24" t="n">
-        <v>6925317</v>
+        <v>6925321</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3241,7 +3237,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120318856</v>
+        <v>120318857</v>
       </c>
       <c r="B25" t="n">
         <v>97930</v>
@@ -3274,17 +3270,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Holmnäset, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>515159</v>
+        <v>515094</v>
       </c>
       <c r="R25" t="n">
-        <v>6925502</v>
+        <v>6925430</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3311,12 +3311,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2023-08-21</t>
+          <t>2023-10-18</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2023-08-21</t>
+          <t>2023-10-18</t>
         </is>
       </c>
       <c r="AD25" t="b">

--- a/artfynd/A 13696-2023 artfynd.xlsx
+++ b/artfynd/A 13696-2023 artfynd.xlsx
@@ -1769,7 +1769,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120318863</v>
+        <v>120318860</v>
       </c>
       <c r="B11" t="n">
         <v>97930</v>
@@ -1804,7 +1804,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1813,10 +1813,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>514693</v>
+        <v>514791</v>
       </c>
       <c r="R11" t="n">
-        <v>6925638</v>
+        <v>6925520</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1875,7 +1875,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120318864</v>
+        <v>120318854</v>
       </c>
       <c r="B12" t="n">
         <v>97930</v>
@@ -1908,21 +1908,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Holmnäset, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>514913</v>
+        <v>515015</v>
       </c>
       <c r="R12" t="n">
-        <v>6925660</v>
+        <v>6925264</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1949,12 +1945,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2023-10-18</t>
+          <t>2023-08-21</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2023-10-18</t>
+          <t>2023-08-21</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1981,7 +1977,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120318853</v>
+        <v>120318863</v>
       </c>
       <c r="B13" t="n">
         <v>97930</v>
@@ -2014,17 +2010,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Holmnäset, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>514985</v>
+        <v>514693</v>
       </c>
       <c r="R13" t="n">
-        <v>6925284</v>
+        <v>6925638</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2051,12 +2051,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2023-08-21</t>
+          <t>2023-10-18</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2023-08-21</t>
+          <t>2023-10-18</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2083,7 +2083,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120318866</v>
+        <v>120318851</v>
       </c>
       <c r="B14" t="n">
         <v>97930</v>
@@ -2118,7 +2118,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2127,10 +2127,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>514990</v>
+        <v>514665</v>
       </c>
       <c r="R14" t="n">
-        <v>6925841</v>
+        <v>6925321</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2189,7 +2189,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120318855</v>
+        <v>120318864</v>
       </c>
       <c r="B15" t="n">
         <v>97930</v>
@@ -2224,7 +2224,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2233,10 +2233,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>515227</v>
+        <v>514913</v>
       </c>
       <c r="R15" t="n">
-        <v>6925317</v>
+        <v>6925660</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2295,7 +2295,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120318854</v>
+        <v>120318856</v>
       </c>
       <c r="B16" t="n">
         <v>97930</v>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>515015</v>
+        <v>515159</v>
       </c>
       <c r="R16" t="n">
-        <v>6925264</v>
+        <v>6925502</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2397,7 +2397,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120318858</v>
+        <v>120318857</v>
       </c>
       <c r="B17" t="n">
         <v>97930</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2441,10 +2441,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>515035</v>
+        <v>515094</v>
       </c>
       <c r="R17" t="n">
-        <v>6925466</v>
+        <v>6925430</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2503,7 +2503,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120318859</v>
+        <v>120318850</v>
       </c>
       <c r="B18" t="n">
         <v>97930</v>
@@ -2536,21 +2536,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Holmnäset, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>515027</v>
+        <v>514866</v>
       </c>
       <c r="R18" t="n">
-        <v>6925459</v>
+        <v>6925169</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2577,12 +2573,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2023-10-18</t>
+          <t>2023-08-21</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2023-10-18</t>
+          <t>2023-08-21</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2609,7 +2605,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120318861</v>
+        <v>120318859</v>
       </c>
       <c r="B19" t="n">
         <v>97930</v>
@@ -2644,7 +2640,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>56</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2653,10 +2649,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>514780</v>
+        <v>515027</v>
       </c>
       <c r="R19" t="n">
-        <v>6925538</v>
+        <v>6925459</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2715,7 +2711,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120318856</v>
+        <v>120318853</v>
       </c>
       <c r="B20" t="n">
         <v>97930</v>
@@ -2755,10 +2751,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>515159</v>
+        <v>514985</v>
       </c>
       <c r="R20" t="n">
-        <v>6925502</v>
+        <v>6925284</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2817,7 +2813,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120318860</v>
+        <v>120318861</v>
       </c>
       <c r="B21" t="n">
         <v>97930</v>
@@ -2852,7 +2848,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>13</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2861,10 +2857,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>514791</v>
+        <v>514780</v>
       </c>
       <c r="R21" t="n">
-        <v>6925520</v>
+        <v>6925538</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2923,7 +2919,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120318862</v>
+        <v>120318858</v>
       </c>
       <c r="B22" t="n">
         <v>97930</v>
@@ -2958,7 +2954,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>27</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2967,10 +2963,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>514696</v>
+        <v>515035</v>
       </c>
       <c r="R22" t="n">
-        <v>6925628</v>
+        <v>6925466</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3029,7 +3025,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120318850</v>
+        <v>120318866</v>
       </c>
       <c r="B23" t="n">
         <v>97930</v>
@@ -3062,17 +3058,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Holmnäset, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>514866</v>
+        <v>514990</v>
       </c>
       <c r="R23" t="n">
-        <v>6925169</v>
+        <v>6925841</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3099,12 +3099,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2023-08-21</t>
+          <t>2023-10-18</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2023-08-21</t>
+          <t>2023-10-18</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3131,7 +3131,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120318851</v>
+        <v>120318862</v>
       </c>
       <c r="B24" t="n">
         <v>97930</v>
@@ -3166,7 +3166,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>18</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3175,10 +3175,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>514665</v>
+        <v>514696</v>
       </c>
       <c r="R24" t="n">
-        <v>6925321</v>
+        <v>6925628</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3237,7 +3237,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120318857</v>
+        <v>120318855</v>
       </c>
       <c r="B25" t="n">
         <v>97930</v>
@@ -3272,7 +3272,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>91</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3281,10 +3281,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>515094</v>
+        <v>515227</v>
       </c>
       <c r="R25" t="n">
-        <v>6925430</v>
+        <v>6925317</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>

--- a/artfynd/A 13696-2023 artfynd.xlsx
+++ b/artfynd/A 13696-2023 artfynd.xlsx
@@ -1769,7 +1769,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120318860</v>
+        <v>120318864</v>
       </c>
       <c r="B11" t="n">
         <v>97930</v>
@@ -1813,10 +1813,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>514791</v>
+        <v>514913</v>
       </c>
       <c r="R11" t="n">
-        <v>6925520</v>
+        <v>6925660</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1875,7 +1875,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120318854</v>
+        <v>120318857</v>
       </c>
       <c r="B12" t="n">
         <v>97930</v>
@@ -1908,17 +1908,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Holmnäset, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>515015</v>
+        <v>515094</v>
       </c>
       <c r="R12" t="n">
-        <v>6925264</v>
+        <v>6925430</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1945,12 +1949,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2023-08-21</t>
+          <t>2023-10-18</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2023-08-21</t>
+          <t>2023-10-18</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1977,7 +1981,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120318863</v>
+        <v>120318858</v>
       </c>
       <c r="B13" t="n">
         <v>97930</v>
@@ -2021,10 +2025,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>514693</v>
+        <v>515035</v>
       </c>
       <c r="R13" t="n">
-        <v>6925638</v>
+        <v>6925466</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2083,7 +2087,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120318851</v>
+        <v>120318850</v>
       </c>
       <c r="B14" t="n">
         <v>97930</v>
@@ -2116,21 +2120,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Holmnäset, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>514665</v>
+        <v>514866</v>
       </c>
       <c r="R14" t="n">
-        <v>6925321</v>
+        <v>6925169</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2157,12 +2157,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2023-10-18</t>
+          <t>2023-08-21</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2023-10-18</t>
+          <t>2023-08-21</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2189,7 +2189,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120318864</v>
+        <v>120318855</v>
       </c>
       <c r="B15" t="n">
         <v>97930</v>
@@ -2224,7 +2224,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>91</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2233,10 +2233,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>514913</v>
+        <v>515227</v>
       </c>
       <c r="R15" t="n">
-        <v>6925660</v>
+        <v>6925317</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2295,7 +2295,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120318856</v>
+        <v>120318859</v>
       </c>
       <c r="B16" t="n">
         <v>97930</v>
@@ -2328,17 +2328,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Holmnäset, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>515159</v>
+        <v>515027</v>
       </c>
       <c r="R16" t="n">
-        <v>6925502</v>
+        <v>6925459</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2365,12 +2369,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2023-08-21</t>
+          <t>2023-10-18</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2023-08-21</t>
+          <t>2023-10-18</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2397,7 +2401,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120318857</v>
+        <v>120318851</v>
       </c>
       <c r="B17" t="n">
         <v>97930</v>
@@ -2432,7 +2436,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2441,10 +2445,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>515094</v>
+        <v>514665</v>
       </c>
       <c r="R17" t="n">
-        <v>6925430</v>
+        <v>6925321</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2503,7 +2507,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120318850</v>
+        <v>120318861</v>
       </c>
       <c r="B18" t="n">
         <v>97930</v>
@@ -2536,17 +2540,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Holmnäset, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>514866</v>
+        <v>514780</v>
       </c>
       <c r="R18" t="n">
-        <v>6925169</v>
+        <v>6925538</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2573,12 +2581,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2023-08-21</t>
+          <t>2023-10-18</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2023-08-21</t>
+          <t>2023-10-18</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2605,7 +2613,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120318859</v>
+        <v>120318866</v>
       </c>
       <c r="B19" t="n">
         <v>97930</v>
@@ -2640,7 +2648,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2649,10 +2657,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>515027</v>
+        <v>514990</v>
       </c>
       <c r="R19" t="n">
-        <v>6925459</v>
+        <v>6925841</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2813,7 +2821,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120318861</v>
+        <v>120318856</v>
       </c>
       <c r="B21" t="n">
         <v>97930</v>
@@ -2846,21 +2854,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Holmnäset, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>514780</v>
+        <v>515159</v>
       </c>
       <c r="R21" t="n">
-        <v>6925538</v>
+        <v>6925502</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2887,12 +2891,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2023-10-18</t>
+          <t>2023-08-21</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2023-10-18</t>
+          <t>2023-08-21</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2919,7 +2923,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120318858</v>
+        <v>120318860</v>
       </c>
       <c r="B22" t="n">
         <v>97930</v>
@@ -2954,7 +2958,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2963,10 +2967,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>515035</v>
+        <v>514791</v>
       </c>
       <c r="R22" t="n">
-        <v>6925466</v>
+        <v>6925520</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3025,7 +3029,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120318866</v>
+        <v>120318854</v>
       </c>
       <c r="B23" t="n">
         <v>97930</v>
@@ -3058,21 +3062,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Holmnäset, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>514990</v>
+        <v>515015</v>
       </c>
       <c r="R23" t="n">
-        <v>6925841</v>
+        <v>6925264</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3099,12 +3099,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2023-10-18</t>
+          <t>2023-08-21</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2023-10-18</t>
+          <t>2023-08-21</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3131,7 +3131,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120318862</v>
+        <v>120318863</v>
       </c>
       <c r="B24" t="n">
         <v>97930</v>
@@ -3166,7 +3166,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>27</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3175,10 +3175,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>514696</v>
+        <v>514693</v>
       </c>
       <c r="R24" t="n">
-        <v>6925628</v>
+        <v>6925638</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3237,7 +3237,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120318855</v>
+        <v>120318862</v>
       </c>
       <c r="B25" t="n">
         <v>97930</v>
@@ -3272,7 +3272,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>18</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3281,10 +3281,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>515227</v>
+        <v>514696</v>
       </c>
       <c r="R25" t="n">
-        <v>6925317</v>
+        <v>6925628</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>

--- a/artfynd/A 13696-2023 artfynd.xlsx
+++ b/artfynd/A 13696-2023 artfynd.xlsx
@@ -1769,7 +1769,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120318864</v>
+        <v>120318856</v>
       </c>
       <c r="B11" t="n">
         <v>97930</v>
@@ -1802,21 +1802,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Holmnäset, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>514913</v>
+        <v>515159</v>
       </c>
       <c r="R11" t="n">
-        <v>6925660</v>
+        <v>6925502</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1843,12 +1839,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2023-10-18</t>
+          <t>2023-08-21</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2023-10-18</t>
+          <t>2023-08-21</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1875,7 +1871,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120318857</v>
+        <v>120318854</v>
       </c>
       <c r="B12" t="n">
         <v>97930</v>
@@ -1908,21 +1904,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Holmnäset, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>515094</v>
+        <v>515015</v>
       </c>
       <c r="R12" t="n">
-        <v>6925430</v>
+        <v>6925264</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1949,12 +1941,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2023-10-18</t>
+          <t>2023-08-21</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2023-10-18</t>
+          <t>2023-08-21</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2087,7 +2079,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120318850</v>
+        <v>120318862</v>
       </c>
       <c r="B14" t="n">
         <v>97930</v>
@@ -2120,17 +2112,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Holmnäset, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>514866</v>
+        <v>514696</v>
       </c>
       <c r="R14" t="n">
-        <v>6925169</v>
+        <v>6925628</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2157,12 +2153,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2023-08-21</t>
+          <t>2023-10-18</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2023-08-21</t>
+          <t>2023-10-18</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2189,7 +2185,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120318855</v>
+        <v>120318863</v>
       </c>
       <c r="B15" t="n">
         <v>97930</v>
@@ -2224,7 +2220,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>27</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2233,10 +2229,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>515227</v>
+        <v>514693</v>
       </c>
       <c r="R15" t="n">
-        <v>6925317</v>
+        <v>6925638</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2295,7 +2291,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120318859</v>
+        <v>120318857</v>
       </c>
       <c r="B16" t="n">
         <v>97930</v>
@@ -2330,7 +2326,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2339,10 +2335,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>515027</v>
+        <v>515094</v>
       </c>
       <c r="R16" t="n">
-        <v>6925459</v>
+        <v>6925430</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2401,7 +2397,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120318851</v>
+        <v>120318861</v>
       </c>
       <c r="B17" t="n">
         <v>97930</v>
@@ -2436,7 +2432,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>13</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2445,10 +2441,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>514665</v>
+        <v>514780</v>
       </c>
       <c r="R17" t="n">
-        <v>6925321</v>
+        <v>6925538</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2507,7 +2503,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120318861</v>
+        <v>120318853</v>
       </c>
       <c r="B18" t="n">
         <v>97930</v>
@@ -2540,21 +2536,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Holmnäset, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>514780</v>
+        <v>514985</v>
       </c>
       <c r="R18" t="n">
-        <v>6925538</v>
+        <v>6925284</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2581,12 +2573,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2023-10-18</t>
+          <t>2023-08-21</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2023-10-18</t>
+          <t>2023-08-21</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2613,7 +2605,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120318866</v>
+        <v>120318851</v>
       </c>
       <c r="B19" t="n">
         <v>97930</v>
@@ -2648,7 +2640,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2657,10 +2649,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>514990</v>
+        <v>514665</v>
       </c>
       <c r="R19" t="n">
-        <v>6925841</v>
+        <v>6925321</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2719,7 +2711,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120318853</v>
+        <v>120318866</v>
       </c>
       <c r="B20" t="n">
         <v>97930</v>
@@ -2752,17 +2744,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Holmnäset, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>514985</v>
+        <v>514990</v>
       </c>
       <c r="R20" t="n">
-        <v>6925284</v>
+        <v>6925841</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2789,12 +2785,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2023-08-21</t>
+          <t>2023-10-18</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2023-08-21</t>
+          <t>2023-10-18</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2821,7 +2817,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120318856</v>
+        <v>120318860</v>
       </c>
       <c r="B21" t="n">
         <v>97930</v>
@@ -2854,17 +2850,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Holmnäset, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>515159</v>
+        <v>514791</v>
       </c>
       <c r="R21" t="n">
-        <v>6925502</v>
+        <v>6925520</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2023-08-21</t>
+          <t>2023-10-18</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2023-08-21</t>
+          <t>2023-10-18</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2923,7 +2923,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120318860</v>
+        <v>120318855</v>
       </c>
       <c r="B22" t="n">
         <v>97930</v>
@@ -2958,7 +2958,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>91</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2967,10 +2967,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>514791</v>
+        <v>515227</v>
       </c>
       <c r="R22" t="n">
-        <v>6925520</v>
+        <v>6925317</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3029,7 +3029,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120318854</v>
+        <v>120318859</v>
       </c>
       <c r="B23" t="n">
         <v>97930</v>
@@ -3062,17 +3062,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Holmnäset, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>515015</v>
+        <v>515027</v>
       </c>
       <c r="R23" t="n">
-        <v>6925264</v>
+        <v>6925459</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3099,12 +3103,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2023-08-21</t>
+          <t>2023-10-18</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2023-08-21</t>
+          <t>2023-10-18</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3131,7 +3135,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120318863</v>
+        <v>120318850</v>
       </c>
       <c r="B24" t="n">
         <v>97930</v>
@@ -3164,21 +3168,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Holmnäset, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>514693</v>
+        <v>514866</v>
       </c>
       <c r="R24" t="n">
-        <v>6925638</v>
+        <v>6925169</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3205,12 +3205,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2023-10-18</t>
+          <t>2023-08-21</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2023-10-18</t>
+          <t>2023-08-21</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3237,7 +3237,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120318862</v>
+        <v>120318864</v>
       </c>
       <c r="B25" t="n">
         <v>97930</v>
@@ -3272,7 +3272,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3281,10 +3281,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>514696</v>
+        <v>514913</v>
       </c>
       <c r="R25" t="n">
-        <v>6925628</v>
+        <v>6925660</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>

--- a/artfynd/A 13696-2023 artfynd.xlsx
+++ b/artfynd/A 13696-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY25"/>
+  <dimension ref="A1:AZ25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111609167</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111609168</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111609174</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1099,6 +1119,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111609169</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1205,6 +1230,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111609170</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1311,6 +1341,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111609173</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1417,6 +1452,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111609176</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1514,6 +1554,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120318850</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1615,6 +1660,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120318851</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1712,6 +1762,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120318853</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1809,6 +1864,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120318854</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1910,6 +1970,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120318855</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2007,6 +2072,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120318856</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2108,6 +2178,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120318857</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2209,6 +2284,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120318858</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2310,6 +2390,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120318859</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2411,6 +2496,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120318860</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2512,6 +2602,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120318861</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2613,6 +2708,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120318862</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2714,6 +2814,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120318863</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2815,6 +2920,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120318864</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2916,6 +3026,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120318866</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3023,6 +3138,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111609172</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3130,8 +3250,39 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111609175</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>